--- a/results/exp05-c100-resnet-bw1-50-fedavg-old/20260924-070058/rounds.xlsx
+++ b/results/exp05-c100-resnet-bw1-50-fedavg-old/20260924-070058/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2693,6 +2693,6148 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:28:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.158573259910731</v>
+      </c>
+      <c r="F28" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="H28" t="n">
+        <v>26</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60.2113</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1:00.21</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>56.5779</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.3656</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.2666</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1655.4173</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>27:35.42</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7,1,4,0,9,2,8,3,6,5</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>7:29;1:35;4:7;0:20;9:10;2:11;8:31;3:12;6:36;5:21</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7:[1,3];1:[3,4,5];4:[];0:[2,3];9:[2];2:[7];8:[3,4,7];3:[5];6:[1,4,7];5:[5,7]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>c7:bw=29,experts=[1,3]; c1:bw=35,experts=[3,4,5]; c4:bw=7,experts=[]; c0:bw=20,experts=[2,3]; c9:bw=10,experts=[2]; c2:bw=11,experts=[7]; c8:bw=31,experts=[3,4,7]; c3:bw=12,experts=[5]; c6:bw=36,experts=[1,4,7]; c5:bw=21,experts=[5,7]</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>5.1999,4.8523,7.4195,5.2120,3.9716,4.1850,5.9225,5.6653,7.3255,6.8242</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:29:34</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.140186193581173</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="G29" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="H29" t="n">
+        <v>26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>60.0838</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:00.08</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>56.6073</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.1828</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.2925</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1715.5189</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>28:35.52</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:17;9:28;0:27;8:17;2:1;5:19;1:14;3:7;4:4;7:1</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[2];9:[4,6];0:[5,7];8:[5];2:[];5:[4];1:[2];3:[];4:[];7:[]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[2]; c9:bw=28,experts=[4,6]; c0:bw=27,experts=[5,7]; c8:bw=17,experts=[5]; c2:bw=1,experts=[]; c5:bw=19,experts=[4]; c1:bw=14,experts=[2]; c3:bw=7,experts=[]; c4:bw=4,experts=[]; c7:bw=1,experts=[]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>7.3834,3.9949,5.2094,5.9244,4.2259,6.8499,4.8011,5.6742,7.4140,5.1301</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:30:34</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.116695798056541</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="H30" t="n">
+        <v>29</v>
+      </c>
+      <c r="I30" t="n">
+        <v>60.3628</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1:00.36</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>56.823</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.2446</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.2938</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1775.8995</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>29:35.90</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:22;0:25;1:19;9:25;6:24;8:19;7:12;3:18;2:10;5:19</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[1,4];0:[1,4];1:[7];9:[4,6];6:[4,6];8:[4];7:[7];3:[2];2:[2];5:[2]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=22,experts=[1,4]; c0:bw=25,experts=[1,4]; c1:bw=19,experts=[7]; c9:bw=25,experts=[4,6]; c6:bw=24,experts=[4,6]; c8:bw=19,experts=[4]; c7:bw=12,experts=[7]; c3:bw=18,experts=[2]; c2:bw=10,experts=[2]; c5:bw=19,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>7.5209,5.2725,4.8284,4.0332,7.3553,5.8607,5.1580,5.7287,4.2304,6.8349</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:31:35</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.020334885135</v>
+      </c>
+      <c r="F31" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" t="n">
+        <v>60.3795</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:00.38</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>56.7808</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.3071</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.2903</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1836.5019</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>30:36.50</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:35;1:20;9:31;4:29;0:10;8:23;6:6;7:7;3:33;2:15</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[0,4,6];1:[4,6];9:[1,4,6];4:[4,6];0:[4];8:[4,6];6:[];7:[];3:[1,4,7];2:[0]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=35,experts=[0,4,6]; c1:bw=20,experts=[4,6]; c9:bw=31,experts=[1,4,6]; c4:bw=29,experts=[4,6]; c0:bw=10,experts=[4]; c8:bw=23,experts=[4,6]; c6:bw=6,experts=[]; c7:bw=7,experts=[]; c3:bw=33,experts=[1,4,7]; c2:bw=15,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>6.9196,4.8667,4.0319,7.4570,5.2173,5.8870,7.3828,5.1429,5.6569,4.2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:32:35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.989487761461128</v>
+      </c>
+      <c r="F32" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="G32" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="H32" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" t="n">
+        <v>60.4749</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1:00.47</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>56.8807</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.2982</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.2948</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1896.9962</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>31:37.00</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:17;4:11;9:25;1:17;5:35;8:19;3:13;2:9;0:27;7:36</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[0];4:[0];9:[4,6];1:[0];5:[1,4,6];8:[2];3:[6];2:[];0:[4,6];7:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[0]; c4:bw=11,experts=[0]; c9:bw=25,experts=[4,6]; c1:bw=17,experts=[0]; c5:bw=35,experts=[1,4,6]; c8:bw=19,experts=[2]; c3:bw=13,experts=[6]; c2:bw=9,experts=[]; c0:bw=27,experts=[4,6]; c7:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>7.4498,7.4589,4.0505,4.7681,6.8731,5.9228,5.7362,4.2116,5.2460,5.1636</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:33:36</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.94556768343388</v>
+      </c>
+      <c r="F33" t="n">
+        <v>47</v>
+      </c>
+      <c r="G33" t="n">
+        <v>47</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32</v>
+      </c>
+      <c r="I33" t="n">
+        <v>60.4278</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:00.43</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>56.9107</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.2335</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.2823</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1957.4419</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>32:37.44</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:12;5:20;4:28;7:27;0:26;1:12;3:16;6:15;2:30;9:18</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[4];5:[4,6];4:[4,6];7:[4,6];0:[4,6];1:[4];3:[4];6:[3];2:[1,3,6];9:[0]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[4]; c5:bw=20,experts=[4,6]; c4:bw=28,experts=[4,6]; c7:bw=27,experts=[4,6]; c0:bw=26,experts=[4,6]; c1:bw=12,experts=[4]; c3:bw=16,experts=[4]; c6:bw=15,experts=[3]; c2:bw=30,experts=[1,3,6]; c9:bw=18,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>5.9507,6.9454,7.4756,5.1386,5.2430,4.8127,5.6788,7.4283,4.2146,4.0230</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:34:36</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.895139552393485</v>
+      </c>
+      <c r="F34" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="G34" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>60.7735</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:00.77</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>57.0481</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.4371</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2018.235</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>33:38.23</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:30;1:19;3:40;6:21;5:17;9:24;2:13;8:28;4:26;0:35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[2,4,6];1:[1];3:[0,4,5,6];6:[4,6];5:[4];9:[3,5];2:[4];8:[1,4];4:[3,5];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=30,experts=[2,4,6]; c1:bw=19,experts=[1]; c3:bw=40,experts=[0,4,5,6]; c6:bw=21,experts=[4,6]; c5:bw=17,experts=[4]; c9:bw=24,experts=[3,5]; c2:bw=13,experts=[4]; c8:bw=28,experts=[1,4]; c4:bw=26,experts=[3,5]; c0:bw=35,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>5.1762,4.8245,5.7718,7.4457,6.8815,4.0082,4.2432,5.9218,7.5131,5.2621</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35:37</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.878070157183866</v>
+      </c>
+      <c r="F35" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>60.7563</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1:00.76</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>57.0195</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.4455</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2079.0103</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>34:39.01</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:26;1:26;6:27;9:38;8:24;0:13;5:34;7:18;3:41;2:30</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[2,7];1:[4,6];6:[4,5];9:[4,6,7];8:[0,4];0:[4];5:[3,4,6];7:[5];3:[0,3,4,6];2:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=26,experts=[2,7]; c1:bw=26,experts=[4,6]; c6:bw=27,experts=[4,5]; c9:bw=38,experts=[4,6,7]; c8:bw=24,experts=[0,4]; c0:bw=13,experts=[4]; c5:bw=34,experts=[3,4,6]; c7:bw=18,experts=[5]; c3:bw=41,experts=[0,3,4,6]; c2:bw=30,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.5291,4.8565,7.3884,4.0134,5.9073,5.2417,6.8916,5.2050,5.7572,4.2292</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:36:38</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.937218319052182</v>
+      </c>
+      <c r="F36" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="G36" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="H36" t="n">
+        <v>34</v>
+      </c>
+      <c r="I36" t="n">
+        <v>60.5989</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:00.60</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>57.0269</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.2931</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.2777</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2139.6293</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>35:39.63</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:19;0:11;1:17;6:25;2:26;8:28;9:15;7:27;5:23;3:14</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[4];0:[2];1:[3];6:[1,7];2:[4,7];8:[3,7];9:[2];7:[1,3];5:[5,7];3:[4]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=19,experts=[4]; c0:bw=11,experts=[2]; c1:bw=17,experts=[3]; c6:bw=25,experts=[1,7]; c2:bw=26,experts=[4,7]; c8:bw=28,experts=[3,7]; c9:bw=15,experts=[2]; c7:bw=27,experts=[1,3]; c5:bw=23,experts=[5,7]; c3:bw=14,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7.4674,5.3176,4.8278,7.4392,4.2412,5.9281,4.0185,5.2329,6.8123,5.7419</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:37:38</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.857310242594898</v>
+      </c>
+      <c r="F37" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="G37" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>60.6403</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:00.64</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>57</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.3675</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.2715</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2200.2911</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>36:40.29</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:21;0:20;3:34;7:15;6:24;5:28;1:5;4:42;8:29;2:29</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[4,6];0:[3,5];3:[0,4,6];7:[4];6:[2,4];5:[4,6];1:[];4:[0,4,5,6];8:[4,5];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[4,6]; c0:bw=20,experts=[3,5]; c3:bw=34,experts=[0,4,6]; c7:bw=15,experts=[4]; c6:bw=24,experts=[2,4]; c5:bw=28,experts=[4,6]; c1:bw=5,experts=[]; c4:bw=42,experts=[0,4,5,6]; c8:bw=29,experts=[4,5]; c2:bw=29,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>4.0154,5.3741,5.7398,5.1619,7.3912,6.8860,4.8023,7.4759,5.9082,4.2451</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:38:40</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.830858575720624</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="G38" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>60.8661</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:00.87</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>57.1889</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.3854</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.2906</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2261.382</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>37:41.38</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:10;5:22;2:20;6:37;4:22;7:24;9:23;0:31;3:20;8:3</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[5];5:[2,4];2:[2,4];6:[0,4,6];4:[1,4];7:[4,7];9:[4,6];0:[1,4,7];3:[2,4];8:[]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[5]; c5:bw=22,experts=[2,4]; c2:bw=20,experts=[2,4]; c6:bw=37,experts=[0,4,6]; c4:bw=22,experts=[1,4]; c7:bw=24,experts=[4,7]; c9:bw=23,experts=[4,6]; c0:bw=31,experts=[1,4,7]; c3:bw=20,experts=[2,4]; c8:bw=3,experts=[]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>4.8430,6.9403,4.2767,7.4604,7.4990,5.1356,4.0325,5.3125,5.7078,5.9812</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:39:40</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.862097049788524</v>
+      </c>
+      <c r="F39" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="G39" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="n">
+        <v>60.8184</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:00.82</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>57.2751</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.2547</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.2872</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2322.223</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>38:42.22</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:26;6:10;4:29;1:18;5:1;2:2;3:22;7:29;9:15;0:23</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[4];4:[4,6];1:[2];5:[];2:[];3:[1,7];7:[4,6];9:[1];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=26,experts=[4,6]; c6:bw=10,experts=[4]; c4:bw=29,experts=[4,6]; c1:bw=18,experts=[2]; c5:bw=1,experts=[]; c2:bw=2,experts=[]; c3:bw=22,experts=[1,7]; c7:bw=29,experts=[4,6]; c9:bw=15,experts=[1]; c0:bw=23,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>5.9863,7.4878,7.5069,4.8189,6.8694,4.2682,5.8213,5.1522,4.0564,5.3078</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:40:41</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.809305874359961</v>
+      </c>
+      <c r="F40" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="H40" t="n">
+        <v>39</v>
+      </c>
+      <c r="I40" t="n">
+        <v>60.7764</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:00.78</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>57.1458</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.3346</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2383.0197</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>39:43.02</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:15;0:2;1:25;7:23;6:17;8:25;2:20;4:20;9:13;5:42</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[4];0:[];1:[0,7];7:[0,4];6:[4];8:[2,4];2:[0,4];4:[4,6];9:[4];5:[0,1,4,6]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=15,experts=[4]; c0:bw=2,experts=[]; c1:bw=25,experts=[0,7]; c7:bw=23,experts=[0,4]; c6:bw=17,experts=[4]; c8:bw=25,experts=[2,4]; c2:bw=20,experts=[0,4]; c4:bw=20,experts=[4,6]; c9:bw=13,experts=[4]; c5:bw=42,experts=[0,1,4,6]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5.8041,5.3352,4.8501,5.1569,7.4157,5.8948,4.2511,7.5397,4.0119,6.8862</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:41:42</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.766252481136406</v>
+      </c>
+      <c r="F41" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="H41" t="n">
+        <v>39</v>
+      </c>
+      <c r="I41" t="n">
+        <v>60.786</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:00.79</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>57.1808</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.3084</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.2954</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2443.8263</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>40:43.83</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:15;1:24;5:18;6:26;2:37;7:38;3:4;4:11;9:22;0:20</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[4];1:[4,6];5:[4];6:[3,4];2:[1,3,4];7:[0,4,6];3:[];4:[4];9:[0,4];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=15,experts=[4]; c1:bw=24,experts=[4,6]; c5:bw=18,experts=[4]; c6:bw=26,experts=[3,4]; c2:bw=37,experts=[1,3,4]; c7:bw=38,experts=[0,4,6]; c3:bw=4,experts=[]; c4:bw=11,experts=[4]; c9:bw=22,experts=[0,4]; c0:bw=20,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>5.9924,4.8733,6.9566,7.4359,4.2338,5.1464,5.7198,7.4625,4.0380,5.3222</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:42:43</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.778475029775953</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="G42" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="H42" t="n">
+        <v>41</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60.975</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:00.97</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>57.2985</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.3833</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.2919</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2504.8253</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>41:44.83</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:30;6:1;8:32;1:5;4:29;5:35;7:39;3:23;9:30;0:1</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[0,4,6];6:[];8:[1,4,6];1:[];4:[3,4];5:[0,4,6];7:[2,4,6];3:[4,5];9:[3,4,5];0:[]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[0,4,6]; c6:bw=1,experts=[]; c8:bw=32,experts=[1,4,6]; c1:bw=5,experts=[]; c4:bw=29,experts=[3,4]; c5:bw=35,experts=[0,4,6]; c7:bw=39,experts=[2,4,6]; c3:bw=23,experts=[4,5]; c9:bw=30,experts=[3,4,5]; c0:bw=1,experts=[]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4.2912,7.5002,5.9891,4.8520,7.5091,6.9010,5.1779,5.7276,4.0423,5.3079</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:43:44</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.781614979403075</v>
+      </c>
+      <c r="F43" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="H43" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" t="n">
+        <v>61.056</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:01.06</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>57.3832</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.3665</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.3051</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2565.903</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>42:45.90</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:29;1:28;3:27;9:29;6:19;0:8;7:11;4:31;8:24;2:23</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[3,4];1:[1,4];3:[3,4];9:[4,7];6:[5];0:[];7:[5];4:[2,4,7];8:[0,4];2:[4,5]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[3,4]; c1:bw=28,experts=[1,4]; c3:bw=27,experts=[3,4]; c9:bw=29,experts=[4,7]; c6:bw=19,experts=[5]; c0:bw=8,experts=[]; c7:bw=11,experts=[5]; c4:bw=31,experts=[2,4,7]; c8:bw=24,experts=[0,4]; c2:bw=23,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>6.9807,4.9049,5.7645,4.0533,7.4730,5.2866,5.2071,7.5112,5.9738,4.2281</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:44:45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.812719717319628</v>
+      </c>
+      <c r="F44" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="G44" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>61.2897</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:01.29</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>57.5988</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.3929</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.2967</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2627.2162</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>43:47.22</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:30;1:33;2:29;8:26;9:18;7:12;4:19;6:7;3:37;0:12</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[4,5,7];1:[3,4,6];2:[4,7];8:[3,7];9:[2];7:[1];4:[4];6:[];3:[0,4,6];0:[0]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=30,experts=[4,5,7]; c1:bw=33,experts=[3,4,6]; c2:bw=29,experts=[4,7]; c8:bw=26,experts=[3,7]; c9:bw=18,experts=[2]; c7:bw=12,experts=[1]; c4:bw=19,experts=[4]; c6:bw=7,experts=[]; c3:bw=37,experts=[0,4,6]; c0:bw=12,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>6.9689,4.8949,4.2914,6.0198,4.0612,5.2064,7.5281,7.5133,5.7743,5.3407</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:45:46</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.770151232945262</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="G45" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>61.0913</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:01.09</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>57.4029</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.4024</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.2846</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2688.3289</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>44:48.33</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:38;3:26;4:16;2:21;7:42;5:14;6:12;9:21;8:19;1:25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[2,3,5];3:[4,6];4:[0];2:[4,6];7:[0,3,4,6];5:[4];6:[1];9:[4,6];8:[5];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[2,3,5]; c3:bw=26,experts=[4,6]; c4:bw=16,experts=[0]; c2:bw=21,experts=[4,6]; c7:bw=42,experts=[0,3,4,6]; c5:bw=14,experts=[4]; c6:bw=12,experts=[1]; c9:bw=21,experts=[4,6]; c8:bw=19,experts=[5]; c1:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5.3573,5.7737,7.5125,4.2896,5.2046,6.9233,7.4243,4.0610,5.9736,4.8828</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:46:48</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.73944254820033</v>
+      </c>
+      <c r="F46" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="G46" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>61.1629</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:01.16</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>57.434</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.4359</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.2916</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2749.5149</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>45:49.51</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:31;0:20;3:38;4:36;7:20;2:28;9:14;6:2;5:25;1:32</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[0,4,6];0:[1,7];3:[2,4,6];4:[1,4,5];7:[4,7];2:[2,4];9:[4];6:[];5:[2,4];1:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=31,experts=[0,4,6]; c0:bw=20,experts=[1,7]; c3:bw=38,experts=[2,4,6]; c4:bw=36,experts=[1,4,5]; c7:bw=20,experts=[4,7]; c2:bw=28,experts=[2,4]; c9:bw=14,experts=[4]; c6:bw=2,experts=[]; c5:bw=25,experts=[2,4]; c1:bw=32,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6.0248,5.2856,5.7787,7.5463,5.2181,4.2656,4.0329,7.4444,6.9432,4.8945</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:47:49</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.719346068077474</v>
+      </c>
+      <c r="F47" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="G47" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>61.327</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:01.33</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>57.6226</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.4132</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.2899</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2810.865</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>46:50.86</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:21;3:15;6:22;1:23;4:36;5:23;2:32;8:22;0:31;7:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[1,4];3:[1];6:[2,7];1:[2,4];4:[0,4,6];5:[4,6];2:[1,4,6];8:[4,6];0:[0,4,6];7:[4]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[1,4]; c3:bw=15,experts=[1]; c6:bw=22,experts=[2,7]; c1:bw=23,experts=[2,4]; c4:bw=36,experts=[0,4,6]; c5:bw=23,experts=[4,6]; c2:bw=32,experts=[1,4,6]; c8:bw=22,experts=[4,6]; c0:bw=31,experts=[0,4,6]; c7:bw=16,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>4.0689,5.8328,7.5265,4.8658,7.5318,6.9479,4.2941,5.9965,5.3497,5.2088</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:48:50</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.706996951673922</v>
+      </c>
+      <c r="F48" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="G48" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>61.2017</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:01.20</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>57.6009</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2872.092</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>47:52.09</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:29;6:13;7:30;9:10;8:22;3:39;4:5;0:26;1:17;2:31</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[1,4];6:[0];7:[0,4,6];9:[4];8:[2,4];3:[4,6,7];4:[];0:[4,6];1:[0];2:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[1,4]; c6:bw=13,experts=[0]; c7:bw=30,experts=[0,4,6]; c9:bw=10,experts=[4]; c8:bw=22,experts=[2,4]; c3:bw=39,experts=[4,6,7]; c4:bw=5,experts=[]; c0:bw=26,experts=[4,6]; c1:bw=17,experts=[0]; c2:bw=31,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>7.0022,7.5327,5.2423,4.0202,5.9857,5.7981,7.5497,5.3518,4.8614,4.2569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:49:52</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.700514161486539</v>
+      </c>
+      <c r="F49" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="G49" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" t="n">
+        <v>61.3561</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:01.36</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>57.6553</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.3837</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2933.471</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>48:53.47</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:28;8:28;4:38;2:32;9:30;6:26;5:31;7:35;0:9;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[4,7];8:[4,6];4:[0,4,6];2:[3,4,6];9:[0,4,6];6:[3,6];5:[0,4,6];7:[0,4,6];0:[];3:[4]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[4,7]; c8:bw=28,experts=[4,6]; c4:bw=38,experts=[0,4,6]; c2:bw=32,experts=[3,4,6]; c9:bw=30,experts=[0,4,6]; c6:bw=26,experts=[3,6]; c5:bw=31,experts=[0,4,6]; c7:bw=35,experts=[0,4,6]; c0:bw=9,experts=[]; c3:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>4.8931,6.0278,7.6087,4.2950,4.0307,7.5053,6.9941,5.2148,5.3335,5.7525</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:50:53</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.702853430632685</v>
+      </c>
+      <c r="F50" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="G50" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="H50" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" t="n">
+        <v>61.427</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:01.43</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>57.7227</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.4021</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2994.9211</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>49:54.92</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:27;3:18;8:15;0:11;2:33;5:32;6:7;7:25;9:30;1:31</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[3,4];3:[5];8:[1];0:[4];2:[0,4,6];5:[0,4,6];6:[];7:[2,4];9:[3,4,5];1:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=27,experts=[3,4]; c3:bw=18,experts=[5]; c8:bw=15,experts=[1]; c0:bw=11,experts=[4]; c2:bw=33,experts=[0,4,6]; c5:bw=32,experts=[0,4,6]; c6:bw=7,experts=[]; c7:bw=25,experts=[2,4]; c9:bw=30,experts=[3,4,5]; c1:bw=31,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.5914,5.8070,6.0041,5.3436,4.3175,6.9761,7.4893,5.2292,4.0640,4.9006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:51:54</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.692754212401617</v>
+      </c>
+      <c r="F51" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="G51" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>61.3103</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:01.31</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>57.701</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.3348</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.2732</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3056.2566</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>50:56.26</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:18;4:4;7:19;6:38;2:36;1:37;3:22;0:16;9:15;5:18</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[4];4:[];7:[5];6:[4,5,6];2:[4,5,6];1:[1,4,6];3:[3,4];0:[4];9:[7];5:[3]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[4]; c4:bw=4,experts=[]; c7:bw=19,experts=[5]; c6:bw=38,experts=[4,5,6]; c2:bw=36,experts=[4,5,6]; c1:bw=37,experts=[1,4,6]; c3:bw=22,experts=[3,4]; c0:bw=16,experts=[4]; c9:bw=15,experts=[7]; c5:bw=18,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>6.0456,7.5912,5.2369,7.4706,4.2790,4.8715,5.8106,5.3465,4.0535,6.9956</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:52:56</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.721601062597623</v>
+      </c>
+      <c r="F52" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="G52" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>61.5025</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:01.50</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>57.8522</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.3766</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3117.7835</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>51:57.78</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:27;0:30;1:12;2:11;8:26;6:29;9:10;3:31;4:6;7:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[5,7];0:[0,4,6];1:[3];2:[7];8:[3,7];6:[4,6];9:[2];3:[0,4,6];4:[];7:[1]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[5,7]; c0:bw=30,experts=[0,4,6]; c1:bw=12,experts=[3]; c2:bw=11,experts=[7]; c8:bw=26,experts=[3,7]; c6:bw=29,experts=[4,6]; c9:bw=10,experts=[2]; c3:bw=31,experts=[0,4,6]; c4:bw=6,experts=[]; c7:bw=15,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>7.0151,5.3940,4.8775,4.2810,6.0158,7.6024,4.0704,5.7897,7.5584,5.2478</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:57</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.699862666627661</v>
+      </c>
+      <c r="F53" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="G53" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>61.2432</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:01.24</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>57.6587</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.2729</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.3104</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3179.0505</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>52:59.05</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:26;8:10;5:14;7:19;1:23;4:19;9:17;6:29;2:17;3:24</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[2,3];8:[5];5:[4];7:[3];1:[4,6];4:[2];9:[4];6:[1,4];2:[4];3:[4,6]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[2,3]; c8:bw=10,experts=[5]; c5:bw=14,experts=[4]; c7:bw=19,experts=[3]; c1:bw=23,experts=[4,6]; c4:bw=19,experts=[2]; c9:bw=17,experts=[4]; c6:bw=29,experts=[1,4]; c2:bw=17,experts=[4]; c3:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5.3926,6.0408,7.0102,5.2513,4.8777,7.5215,4.0361,7.4234,4.2900,5.8151</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:54:59</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.67920416734827</v>
+      </c>
+      <c r="F54" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="G54" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="H54" t="n">
+        <v>53</v>
+      </c>
+      <c r="I54" t="n">
+        <v>61.6171</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:01.62</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>57.8968</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.4208</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.2982</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3240.691</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>54:00.69</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:12;4:16;5:25;1:33;3:27;9:35;6:20;7:25;0:22;2:29</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[0];4:[7];5:[2,4];1:[4,5,6];3:[2,4];9:[4,5,6];6:[4,6];7:[4,7];0:[1,5];2:[2,4]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[0]; c4:bw=16,experts=[7]; c5:bw=25,experts=[2,4]; c1:bw=33,experts=[4,5,6]; c3:bw=27,experts=[2,4]; c9:bw=35,experts=[4,5,6]; c6:bw=20,experts=[4,6]; c7:bw=25,experts=[4,7]; c0:bw=22,experts=[1,5]; c2:bw=29,experts=[2,4]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>6.0780,7.6035,7.0257,4.9141,5.8111,4.0898,7.5035,5.2131,5.3619,4.2959</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:56:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.656833678182283</v>
+      </c>
+      <c r="F55" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="G55" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="H55" t="n">
+        <v>53</v>
+      </c>
+      <c r="I55" t="n">
+        <v>61.5655</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:01.57</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>57.9075</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.3384</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.3183</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3302.2802</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>55:02.28</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:5;1:30;8:31;7:34;3:17;0:21;6:31;5:2;9:29;4:18</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[];1:[2,4,6];8:[0,4,6];7:[1,4,6];3:[1];0:[4,7];6:[2,4,7];5:[];9:[1,4];4:[1]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=5,experts=[]; c1:bw=30,experts=[2,4,6]; c8:bw=31,experts=[0,4,6]; c7:bw=34,experts=[1,4,6]; c3:bw=17,experts=[1]; c0:bw=21,experts=[4,7]; c6:bw=31,experts=[2,4,7]; c5:bw=2,experts=[]; c9:bw=29,experts=[1,4]; c4:bw=18,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4.3298,4.9359,6.0756,5.2531,5.8532,5.4030,7.4714,6.9317,4.0942,7.5596</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:57:02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.627500824701658</v>
+      </c>
+      <c r="F56" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="G56" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>61.6393</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:01.64</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>58.001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.3418</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.2953</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3363.9438</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>56:03.94</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:31;2:23;4:8;3:30;8:8;5:30;1:34;6:24;0:16;9:35</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[0,4,6];2:[1,4];4:[];3:[4,6,7];8:[];5:[1,4,6];1:[0,4,6];6:[0,4];0:[4];9:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=31,experts=[0,4,6]; c2:bw=23,experts=[1,4]; c4:bw=8,experts=[]; c3:bw=30,experts=[4,6,7]; c8:bw=8,experts=[]; c5:bw=30,experts=[1,4,6]; c1:bw=34,experts=[0,4,6]; c6:bw=24,experts=[0,4]; c0:bw=16,experts=[4]; c9:bw=35,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>5.3333,4.3098,7.5857,5.8321,6.0543,7.0238,4.9026,7.5362,5.3395,4.0836</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:58:04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.644995552438344</v>
+      </c>
+      <c r="F57" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="G57" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>61.5972</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:01.60</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>57.9956</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.2953</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3425.5661</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>57:05.57</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:29;1:32;3:5;2:30;5:17;4:5;8:8;7:10;6:13;0:40</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[4,6];1:[4,6,7];3:[];2:[3,4,6];5:[4];4:[];8:[];7:[4];6:[3];0:[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[4,6]; c1:bw=32,experts=[4,6,7]; c3:bw=5,experts=[]; c2:bw=30,experts=[3,4,6]; c5:bw=17,experts=[4]; c4:bw=5,experts=[]; c8:bw=8,experts=[]; c7:bw=10,experts=[4]; c6:bw=13,experts=[3]; c0:bw=40,experts=[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>4.0950,4.9095,5.8698,4.3080,6.9563,7.6413,6.0716,5.2522,7.5322,5.3596</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:59:06</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.654897682606544</v>
+      </c>
+      <c r="F58" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>57</v>
+      </c>
+      <c r="I58" t="n">
+        <v>61.9969</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:02.00</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>58.2688</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.4264</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3487.5883</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>58:07.59</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:36;8:24;6:27;1:28;7:39;0:40;5:25;4:23;2:19;9:11</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[4,5,6];8:[1,2];6:[4,6];1:[4,6];7:[2,4,6];0:[0,2,4,6];5:[0,4];4:[0,5];2:[0];9:[3]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=36,experts=[4,5,6]; c8:bw=24,experts=[1,2]; c6:bw=27,experts=[4,6]; c1:bw=28,experts=[4,6]; c7:bw=39,experts=[2,4,6]; c0:bw=40,experts=[0,2,4,6]; c5:bw=25,experts=[0,4]; c4:bw=23,experts=[0,5]; c2:bw=19,experts=[0]; c9:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>5.8630,6.1063,7.5514,4.9023,5.2924,5.4133,7.0442,7.6921,4.3137,4.0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00:08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.643478442391239</v>
+      </c>
+      <c r="F59" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="G59" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="H59" t="n">
+        <v>58</v>
+      </c>
+      <c r="I59" t="n">
+        <v>61.7558</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:01.76</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>58.1125</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2.3462</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.2957</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3549.37</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>59:09.37</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:14;2:2;9:32;6:31;5:20;1:17;8:22;4:22;3:35;0:27</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[5];2:[];9:[4,6,7];6:[4,5,6];5:[3,4];1:[1];8:[4,6];4:[3,6];3:[3,4,6];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=14,experts=[5]; c2:bw=2,experts=[]; c9:bw=32,experts=[4,6,7]; c6:bw=31,experts=[4,5,6]; c5:bw=20,experts=[3,4]; c1:bw=17,experts=[1]; c8:bw=22,experts=[4,6]; c4:bw=22,experts=[3,6]; c3:bw=35,experts=[3,4,6]; c0:bw=27,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>5.2570,4.3599,4.0972,7.5464,7.0210,4.9020,6.0693,7.6902,5.8361,5.3336</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:01:09</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.618223465075749</v>
+      </c>
+      <c r="F60" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="G60" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="H60" t="n">
+        <v>59</v>
+      </c>
+      <c r="I60" t="n">
+        <v>61.589</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:01.59</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>57.9758</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.3249</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.2871</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3610.9846</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1:00:10.98</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:21;8:31;9:16;6:11;1:37;4:15;7:16;5:18;0:29;3:20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[5,7];8:[3,4,7];9:[2];6:[4];1:[3,4,6];4:[4];7:[4];5:[5];0:[4,6];3:[0,4]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=21,experts=[5,7]; c8:bw=31,experts=[3,4,7]; c9:bw=16,experts=[2]; c6:bw=11,experts=[4]; c1:bw=37,experts=[3,4,6]; c4:bw=15,experts=[4]; c7:bw=16,experts=[4]; c5:bw=18,experts=[5]; c0:bw=29,experts=[4,6]; c3:bw=20,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>4.3892,6.0825,4.0913,7.5207,4.8957,7.5938,5.2751,6.9435,5.3429,5.8411</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:02:11</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.614919063655941</v>
+      </c>
+      <c r="F61" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="G61" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="H61" t="n">
+        <v>60</v>
+      </c>
+      <c r="I61" t="n">
+        <v>61.7491</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1:01.75</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>58.0597</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.3952</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3672.7599</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1:01:12.76</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:30;7:27;4:17;2:17;5:19;8:14;6:34;9:4;1:31;3:25</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[3,4,6];7:[3,4];4:[2];2:[4];5:[7];8:[5];6:[1,4,6];9:[];1:[0,4,6];3:[4,6]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=30,experts=[3,4,6]; c7:bw=27,experts=[3,4]; c4:bw=17,experts=[2]; c2:bw=17,experts=[4]; c5:bw=19,experts=[7]; c8:bw=14,experts=[5]; c6:bw=34,experts=[1,4,6]; c9:bw=4,experts=[]; c1:bw=31,experts=[0,4,6]; c3:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>5.3861,5.2972,7.6663,4.3575,6.9871,6.0844,7.4511,4.0755,4.9239,5.8307</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:03:13</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.586813878530591</v>
+      </c>
+      <c r="F62" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="G62" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="H62" t="n">
+        <v>61</v>
+      </c>
+      <c r="I62" t="n">
+        <v>61.8104</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1:01.81</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>58.0827</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.4202</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.3062</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3734.5963</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:02:14.60</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:28;6:21;2:16;9:21;1:19;3:24;8:31;4:22;7:25;0:34</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[2,4];6:[4,6];2:[2];9:[4,5];1:[5];3:[2,4];8:[0,4,6];4:[4,7];7:[4,7];0:[1,4,6]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=28,experts=[2,4]; c6:bw=21,experts=[4,6]; c2:bw=16,experts=[2]; c9:bw=21,experts=[4,5]; c1:bw=19,experts=[5]; c3:bw=24,experts=[2,4]; c8:bw=31,experts=[0,4,6]; c4:bw=22,experts=[4,7]; c7:bw=25,experts=[4,7]; c0:bw=34,experts=[1,4,6]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>7.0152,7.5914,4.3460,4.0341,4.9328,5.8694,6.0604,7.5916,5.2733,5.3683</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:04:15</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.596096420069818</v>
+      </c>
+      <c r="F63" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="G63" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="H63" t="n">
+        <v>61</v>
+      </c>
+      <c r="I63" t="n">
+        <v>61.8134</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1:01.81</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>58.1197</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2.387</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.3053</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3796.4366</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:03:16.44</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:7;6:35;9:9;4:34;5:38;0:16;3:30;2:24;1:42;7:25</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[];6:[2,4,7];9:[];4:[1,4,6];5:[0,4,6];0:[7];3:[1,4,6];2:[4,6];1:[0,2,4,6];7:[1,4]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=7,experts=[]; c6:bw=35,experts=[2,4,7]; c9:bw=9,experts=[]; c4:bw=34,experts=[1,4,6]; c5:bw=38,experts=[0,4,6]; c0:bw=16,experts=[7]; c3:bw=30,experts=[1,4,6]; c2:bw=24,experts=[4,6]; c1:bw=42,experts=[0,2,4,6]; c7:bw=25,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>6.0682,7.5585,4.0947,7.6298,6.9963,5.3663,5.8286,4.3296,4.9330,5.3146</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:05:16</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.591033294633156</v>
+      </c>
+      <c r="F64" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="G64" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="H64" t="n">
+        <v>61</v>
+      </c>
+      <c r="I64" t="n">
+        <v>61.7487</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:01.75</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>58.1716</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2.2848</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3858.2127</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:04:18.21</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:5;9:12;6:19;3:30;8:18;1:28;7:39;0:23;2:16;4:30</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[];9:[1];6:[0];3:[4,6,7];8:[4];1:[4,6];7:[0,4,6];0:[4,6];2:[1];4:[1,4,6]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=5,experts=[]; c9:bw=12,experts=[1]; c6:bw=19,experts=[0]; c3:bw=30,experts=[4,6,7]; c8:bw=18,experts=[4]; c1:bw=28,experts=[4,6]; c7:bw=39,experts=[0,4,6]; c0:bw=23,experts=[4,6]; c2:bw=16,experts=[1]; c4:bw=30,experts=[1,4,6]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>7.0560,4.1069,7.5385,5.8444,6.0269,4.9165,5.2816,5.3707,4.3701,7.6601</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.569824024772415</v>
+      </c>
+      <c r="F65" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="G65" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>61.7807</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:01.78</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>58.0909</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.3887</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.2998</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3920.0208</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:05:20.02</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:28;4:21;5:13;3:21;7:19;0:18;8:30;9:34;2:32;1:16</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[3,4];4:[4,6];5:[1];3:[4,6];7:[4];0:[5];8:[0,4,6];9:[0,4,6];2:[3,4,6];1:[7]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=28,experts=[3,4]; c4:bw=21,experts=[4,6]; c5:bw=13,experts=[1]; c3:bw=21,experts=[4,6]; c7:bw=19,experts=[4]; c0:bw=18,experts=[5]; c8:bw=30,experts=[0,4,6]; c9:bw=34,experts=[0,4,6]; c2:bw=32,experts=[3,4,6]; c1:bw=16,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>7.5268,7.6780,6.9967,5.8293,5.2469,5.3862,6.0588,4.0569,4.3927,4.9187</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:07:20</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.577000511037708</v>
+      </c>
+      <c r="F66" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="G66" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="H66" t="n">
+        <v>65</v>
+      </c>
+      <c r="I66" t="n">
+        <v>61.769</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:01.77</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>58.0617</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3981.8163</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:06:21.82</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:5;5:16;4:32;6:28;8:37;3:24;0:23;2:16;1:33;9:26</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[];5:[4];4:[0,4,5];6:[4,6];8:[1,2,4];3:[4,5];0:[0,2];2:[0];1:[0,4,6];9:[3,4]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=5,experts=[]; c5:bw=16,experts=[4]; c4:bw=32,experts=[0,4,5]; c6:bw=28,experts=[4,6]; c8:bw=37,experts=[1,2,4]; c3:bw=24,experts=[4,5]; c0:bw=23,experts=[0,2]; c2:bw=16,experts=[0]; c1:bw=33,experts=[0,4,6]; c9:bw=26,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>5.3039,7.0160,7.6568,7.5148,6.0316,5.8000,5.4017,4.3690,4.9285,4.0393</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:08:22</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.577400738857212</v>
+      </c>
+      <c r="F67" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="G67" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="H67" t="n">
+        <v>65</v>
+      </c>
+      <c r="I67" t="n">
+        <v>61.8005</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:01.80</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>58.1211</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.3803</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4043.6441</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:07:23.64</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:23;5:10;1:31;8:14;9:18;6:17;4:23;0:21;3:38;7:28</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[4,6];5:[3];1:[1,4,6];8:[4];9:[7];6:[5];4:[3,4];0:[4,6];3:[3,4,6];7:[2,5]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=23,experts=[4,6]; c5:bw=10,experts=[3]; c1:bw=31,experts=[1,4,6]; c8:bw=14,experts=[4]; c9:bw=18,experts=[7]; c6:bw=17,experts=[5]; c4:bw=23,experts=[3,4]; c0:bw=21,experts=[4,6]; c3:bw=38,experts=[3,4,6]; c7:bw=28,experts=[2,5]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>4.3564,6.9913,5.0178,6.0461,4.0773,7.5203,7.6156,5.4107,5.8372,5.2484</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:09:24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.543333598662645</v>
+      </c>
+      <c r="F68" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="G68" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="H68" t="n">
+        <v>67</v>
+      </c>
+      <c r="I68" t="n">
+        <v>61.9303</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:01.93</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>58.2123</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2.4347</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4105.6025</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:08:25.60</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:29;5:27;1:21;3:14;6:30;0:18;2:24;9:34;7:33;8:5</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[4,6];5:[4,5];1:[3,4];3:[0];6:[0,4,6];0:[4];2:[5,7];9:[2,4,6];7:[1,4,6];8:[]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[4,6]; c5:bw=27,experts=[4,5]; c1:bw=21,experts=[3,4]; c3:bw=14,experts=[0]; c6:bw=30,experts=[0,4,6]; c0:bw=18,experts=[4]; c2:bw=24,experts=[5,7]; c9:bw=34,experts=[2,4,6]; c7:bw=33,experts=[1,4,6]; c8:bw=5,experts=[]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>7.7029,7.0432,4.9737,5.8301,7.5368,5.3720,4.3324,4.0568,5.2916,6.0726</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:10:25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.573254909593951</v>
+      </c>
+      <c r="F69" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="G69" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="H69" t="n">
+        <v>67</v>
+      </c>
+      <c r="I69" t="n">
+        <v>61.5524</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:01.55</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>57.941</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2.3169</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.2933</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4167.1832</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:09:27.18</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:24;8:18;2:33;0:17;3:15;4:28;5:25;9:9;7:16;6:18</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[4,6];8:[3];2:[0,4,6];0:[3];3:[4];4:[2,4];5:[4,7];9:[];7:[3];6:[1]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=24,experts=[4,6]; c8:bw=18,experts=[3]; c2:bw=33,experts=[0,4,6]; c0:bw=17,experts=[3]; c3:bw=15,experts=[4]; c4:bw=28,experts=[2,4]; c5:bw=25,experts=[4,7]; c9:bw=9,experts=[]; c7:bw=16,experts=[3]; c6:bw=18,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>4.9432,6.0544,4.3593,5.3998,5.8229,7.6000,6.9677,4.0810,5.2142,7.4983</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:11:27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.536009737280664</v>
+      </c>
+      <c r="F70" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="G70" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
+      <c r="I70" t="n">
+        <v>62.0446</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:02.04</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>58.3422</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.3061</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4229.2575</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:10:29.26</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:23;7:33;1:18;4:23;9:20;5:22;0:30;2:38;8:24;6:15</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[2,4];7:[4,6,7];1:[5];4:[4,7];9:[4,5];5:[2,4];0:[1,4,6];2:[2,4,6];8:[5,7];6:[4]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=23,experts=[2,4]; c7:bw=33,experts=[4,6,7]; c1:bw=18,experts=[5]; c4:bw=23,experts=[4,7]; c9:bw=20,experts=[4,5]; c5:bw=22,experts=[2,4]; c0:bw=30,experts=[1,4,6]; c2:bw=38,experts=[2,4,6]; c8:bw=24,experts=[5,7]; c6:bw=15,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>5.9097,5.3462,4.9619,7.6371,4.0864,6.9930,5.4209,4.3538,6.1030,7.5301</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:12:29</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.555256383213313</v>
+      </c>
+      <c r="F71" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="G71" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="H71" t="n">
+        <v>69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>61.9675</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:01.97</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>58.3635</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2.2817</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.3209</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4291.2537</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:11:31.25</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:14;9:1;7:16;3:18;0:17;6:15;2:31;4:33;5:13;8:27</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[2];9:[];7:[4];3:[1];0:[7];6:[2];2:[1,4,6];4:[0,4,6];5:[0];8:[4,6]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=14,experts=[2]; c9:bw=1,experts=[]; c7:bw=16,experts=[4]; c3:bw=18,experts=[1]; c0:bw=17,experts=[7]; c6:bw=15,experts=[2]; c2:bw=31,experts=[1,4,6]; c4:bw=33,experts=[0,4,6]; c5:bw=13,experts=[0]; c8:bw=27,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>5.0013,4.1248,5.3288,5.8672,5.4481,7.5022,4.3373,7.6676,7.0079,6.0783</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:13:31</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.535861104156407</v>
+      </c>
+      <c r="F72" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="G72" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="H72" t="n">
+        <v>71</v>
+      </c>
+      <c r="I72" t="n">
+        <v>61.9437</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:01.94</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>58.3257</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4353.2273</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:12:33.23</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:24;0:9;1:30;9:23;7:12;5:19;3:35;6:28;8:22;2:34</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[1,4];0:[];1:[0,4,6];9:[1,4];7:[0];5:[6];3:[4,6,7];6:[4,7];8:[4,6];2:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=24,experts=[1,4]; c0:bw=9,experts=[]; c1:bw=30,experts=[0,4,6]; c9:bw=23,experts=[1,4]; c7:bw=12,experts=[0]; c5:bw=19,experts=[6]; c3:bw=35,experts=[4,6,7]; c6:bw=28,experts=[4,7]; c8:bw=22,experts=[4,6]; c2:bw=34,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>7.7078,5.4472,5.0106,4.1029,5.3036,6.9955,5.8433,7.4770,6.0920,4.3458</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:14:33</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.514463371348079</v>
+      </c>
+      <c r="F73" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="G73" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="H73" t="n">
+        <v>71</v>
+      </c>
+      <c r="I73" t="n">
+        <v>61.9514</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:01.95</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>58.2889</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2.3633</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4415.2086</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:13:35.21</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:17;1:22;5:24;7:27;6:11;0:30;3:13;2:13;9:21;4:22</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0];1:[4,7];5:[1,4];7:[4,6];6:[3];0:[4,5,6];3:[4];2:[3];9:[0,4];4:[4,6]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=17,experts=[0]; c1:bw=22,experts=[4,7]; c5:bw=24,experts=[1,4]; c7:bw=27,experts=[4,6]; c6:bw=11,experts=[3]; c0:bw=30,experts=[4,5,6]; c3:bw=13,experts=[4]; c2:bw=13,experts=[3]; c9:bw=21,experts=[0,4]; c4:bw=22,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>6.0959,4.9658,7.0303,5.2965,7.5312,5.4419,5.8248,4.3446,4.1231,7.6347</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:15:35</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.504873245528897</v>
+      </c>
+      <c r="F74" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="G74" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H74" t="n">
+        <v>73</v>
+      </c>
+      <c r="I74" t="n">
+        <v>61.913</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:01.91</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>58.3042</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2.3111</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.2942</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4477.1507</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:14:37.15</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:27;8:6;3:22;1:37;5:10;9:29;0:16;7:21;6:11;4:23</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[4,6];8:[];3:[4,5];1:[1,4,6];5:[4];9:[3,4];0:[0];7:[4,6];6:[4];4:[4,5]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=27,experts=[4,6]; c8:bw=6,experts=[]; c3:bw=22,experts=[4,5]; c1:bw=37,experts=[1,4,6]; c5:bw=10,experts=[4]; c9:bw=29,experts=[3,4]; c0:bw=16,experts=[0]; c7:bw=21,experts=[4,6]; c6:bw=11,experts=[4]; c4:bw=23,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>4.3535,6.1150,5.8978,4.9716,7.0448,4.0695,5.4377,5.2952,7.4757,7.6432</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:16:37</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.524628901992029</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H75" t="n">
+        <v>73</v>
+      </c>
+      <c r="I75" t="n">
+        <v>61.9141</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:01.91</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>58.3678</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.2451</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4539.0947</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:15:39.09</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:4;0:22;1:16;5:28;7:37;8:16;6:5;2:3;4:27;9:18</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[];0:[2,4];1:[4];5:[3,4];7:[2,4,5];8:[1];6:[];2:[];4:[3,4];9:[7]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=4,experts=[]; c0:bw=22,experts=[2,4]; c1:bw=16,experts=[4]; c5:bw=28,experts=[3,4]; c7:bw=37,experts=[2,4,5]; c8:bw=16,experts=[1]; c6:bw=5,experts=[]; c2:bw=3,experts=[]; c4:bw=27,experts=[3,4]; c9:bw=18,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>5.9323,5.4000,4.9557,7.0478,5.3254,6.1361,7.5261,4.3169,7.6216,4.1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:17:39</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.521389782186369</v>
+      </c>
+      <c r="F76" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="G76" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H76" t="n">
+        <v>73</v>
+      </c>
+      <c r="I76" t="n">
+        <v>62.1611</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:02.16</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>58.3709</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2.4844</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4601.2863</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:16:41.29</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:22;9:35;1:31;3:11;7:16;6:32;5:18;4:32;0:34;8:30</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[5,7];9:[2,4,6];1:[3,4,6];3:[3];7:[1];6:[0,5,6];5:[5];4:[0,4,6];0:[0,4,6];8:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=22,experts=[5,7]; c9:bw=35,experts=[2,4,6]; c1:bw=31,experts=[3,4,6]; c3:bw=11,experts=[3]; c7:bw=16,experts=[1]; c6:bw=32,experts=[0,5,6]; c5:bw=18,experts=[5]; c4:bw=32,experts=[0,4,6]; c0:bw=34,experts=[0,4,6]; c8:bw=30,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>4.3845,4.0891,4.9843,5.8514,5.3403,7.5852,6.9544,7.6333,5.4281,6.1202</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:42</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.507052945046442</v>
+      </c>
+      <c r="F77" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="G77" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H77" t="n">
+        <v>73</v>
+      </c>
+      <c r="I77" t="n">
+        <v>62.0741</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:02.07</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>58.3963</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2.3702</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.3064</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4663.5953</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:17:43.60</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:16;5:21;0:18;3:8;2:14;6:13;7:38;4:34;9:32;1:30</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[3];5:[4,7];0:[3];3:[];2:[4];6:[1];7:[3,4,6];4:[2,4,6];9:[0,4,6];1:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[3]; c5:bw=21,experts=[4,7]; c0:bw=18,experts=[3]; c3:bw=8,experts=[]; c2:bw=14,experts=[4]; c6:bw=13,experts=[1]; c7:bw=38,experts=[3,4,6]; c4:bw=34,experts=[2,4,6]; c9:bw=32,experts=[0,4,6]; c1:bw=30,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>6.1133,7.0421,5.4238,5.8672,4.3405,7.5606,5.3112,7.6656,4.1019,4.9701</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:19:44</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.520148460440418</v>
+      </c>
+      <c r="F78" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="G78" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H78" t="n">
+        <v>73</v>
+      </c>
+      <c r="I78" t="n">
+        <v>61.9976</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:02.00</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>58.3714</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2.3316</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.2934</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4725.6228</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:18:45.62</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:16;2:19;1:35;8:1;4:2;7:5;6:32;0:36;3:23;5:34</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[5];2:[2];1:[4,5,6];8:[];4:[];7:[];6:[0,4,6];0:[1,4,6];3:[0,2];5:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=16,experts=[5]; c2:bw=19,experts=[2]; c1:bw=35,experts=[4,5,6]; c8:bw=1,experts=[]; c4:bw=2,experts=[]; c7:bw=5,experts=[]; c6:bw=32,experts=[0,4,6]; c0:bw=36,experts=[1,4,6]; c3:bw=23,experts=[0,2]; c5:bw=34,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>4.1160,4.3960,5.0123,6.1212,7.6118,5.2820,7.4798,5.4088,5.8881,7.0553</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:20:46</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.478998718611302</v>
+      </c>
+      <c r="F79" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="G79" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="H79" t="n">
+        <v>78</v>
+      </c>
+      <c r="I79" t="n">
+        <v>62.2711</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:02.27</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>58.5736</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2.3817</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4787.9251</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:19:47.93</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:15;4:13;3:21;7:21;8:31;1:23;9:17;6:33;5:36;2:20</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[7];4:[7];3:[1,4];7:[4,7];8:[4,5,7];1:[2,4];9:[4];6:[2,4,6];5:[0,4,6];2:[1,4]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[7]; c4:bw=13,experts=[7]; c3:bw=21,experts=[1,4]; c7:bw=21,experts=[4,7]; c8:bw=31,experts=[4,5,7]; c1:bw=23,experts=[2,4]; c9:bw=17,experts=[4]; c6:bw=33,experts=[2,4,6]; c5:bw=36,experts=[0,4,6]; c2:bw=20,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>5.4429,7.7163,5.8774,5.3013,6.0994,4.9936,4.0967,7.5876,7.0945,4.3638</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21:49</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.488272263312332</v>
+      </c>
+      <c r="F80" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="G80" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="H80" t="n">
+        <v>78</v>
+      </c>
+      <c r="I80" t="n">
+        <v>62.3989</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:02.40</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>58.7843</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2.3068</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.3065</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4850.3545</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:20:50.35</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:12;9:5;0:20;4:48;7:26;8:25;5:30;3:15;1:21;2:19</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[7];9:[];0:[4,6];4:[0,1,4,6];7:[0,4];8:[4,6];5:[0,4,6];3:[6];1:[4,6];2:[0]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=12,experts=[7]; c9:bw=5,experts=[]; c0:bw=20,experts=[4,6]; c4:bw=48,experts=[0,1,4,6]; c7:bw=26,experts=[0,4]; c8:bw=25,experts=[4,6]; c5:bw=30,experts=[0,4,6]; c3:bw=15,experts=[6]; c1:bw=21,experts=[4,6]; c2:bw=19,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>7.6072,4.1113,5.4660,7.7540,5.3738,6.1489,7.0783,5.8729,4.9837,4.3882</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:22:51</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.473367479430693</v>
+      </c>
+      <c r="F81" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="G81" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="n">
+        <v>62.4294</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:02.43</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>58.7035</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2.4149</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.3097</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4912.8157</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:21:52.82</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:37;9:30;7:27;1:17;3:18;4:32;2:25;0:27;6:22;8:29</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[1,4,6];9:[0,1,4];7:[4,6];1:[7];3:[7];4:[0,4,6];2:[3,4];0:[4,5];6:[3,4];8:[0,4]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=37,experts=[1,4,6]; c9:bw=30,experts=[0,1,4]; c7:bw=27,experts=[4,6]; c1:bw=17,experts=[7]; c3:bw=18,experts=[7]; c4:bw=32,experts=[0,4,6]; c2:bw=25,experts=[3,4]; c0:bw=27,experts=[4,5]; c6:bw=22,experts=[3,4]; c8:bw=29,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>7.0612,4.1237,5.3642,5.0288,5.8856,7.7343,4.3687,5.4060,7.5863,6.1445</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:23:53</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.457445557823519</v>
+      </c>
+      <c r="F82" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="G82" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
+      <c r="I82" t="n">
+        <v>62.339</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:02.34</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>58.6262</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2.3947</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.3168</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4975.1863</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:22:55.19</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:29;2:25;3:38;1:28;4:24;5:17;9:15;7:33;8:27;0:28</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[4,6];2:[4,6];3:[4,5,6];1:[1,4];4:[4,5];5:[4];9:[3];7:[0,4,6];8:[4,6];0:[0,4]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[4,6]; c2:bw=25,experts=[4,6]; c3:bw=38,experts=[4,5,6]; c1:bw=28,experts=[1,4]; c4:bw=24,experts=[4,5]; c5:bw=17,experts=[4]; c9:bw=15,experts=[3]; c7:bw=33,experts=[0,4,6]; c8:bw=27,experts=[4,6]; c0:bw=28,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>7.6105,4.3572,5.8996,5.0348,7.7056,7.0335,4.0961,5.2971,6.1447,5.4470</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:24:56</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.458329674813282</v>
+      </c>
+      <c r="F83" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="G83" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="H83" t="n">
+        <v>82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>62.2868</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:02.29</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>58.5664</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.3091</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5037.5044</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:23:57.50</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:36;0:17;6:21;8:33;7:23;3:22;2:17;9:32;5:23;4:17</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[0,4,6];0:[2];6:[4,6];8:[1,4,6];7:[2,5];3:[4,6];2:[4];9:[4,6,7];5:[3,4];4:[3]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=36,experts=[0,4,6]; c0:bw=17,experts=[2]; c6:bw=21,experts=[4,6]; c8:bw=33,experts=[1,4,6]; c7:bw=23,experts=[2,5]; c3:bw=22,experts=[4,6]; c2:bw=17,experts=[4]; c9:bw=32,experts=[4,6,7]; c5:bw=23,experts=[3,4]; c4:bw=17,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>5.0320,5.4679,7.5835,6.1144,5.2608,5.8738,4.3694,4.1157,7.0416,7.7073</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:25:58</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.463952353381757</v>
+      </c>
+      <c r="F84" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="G84" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="H84" t="n">
+        <v>82</v>
+      </c>
+      <c r="I84" t="n">
+        <v>62.343</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:02.34</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>58.6719</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2.371</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.2989</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5099.8825</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:24:59.88</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:29;4:6;2:23;7:21;5:1;0:1;6:30;1:36;8:22;3:24</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[2,4];4:[];2:[5,7];7:[1,4];5:[];0:[];6:[4,5,6];1:[0,3,4];8:[2,4];3:[3,4]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[2,4]; c4:bw=6,experts=[]; c2:bw=23,experts=[5,7]; c7:bw=21,experts=[1,4]; c5:bw=1,experts=[]; c0:bw=1,experts=[]; c6:bw=30,experts=[4,5,6]; c1:bw=36,experts=[0,3,4]; c8:bw=22,experts=[2,4]; c3:bw=24,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.1277,7.6977,4.4328,5.3476,7.0535,5.4338,7.6097,4.9927,6.1046,5.8718</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:27:00</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.460511560413294</v>
+      </c>
+      <c r="F85" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="G85" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="H85" t="n">
+        <v>82</v>
+      </c>
+      <c r="I85" t="n">
+        <v>62.157</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:02.16</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>58.6154</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2.2465</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.2939</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5162.0724</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:26:02.07</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:38;3:18;1:33;6:2;9:12;2:21;7:27;5:11;4:16;0:6</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[3,4,6];3:[4];1:[0,4,6];6:[];9:[4];2:[4,6];7:[3,4];5:[5];4:[2];0:[]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=38,experts=[3,4,6]; c3:bw=18,experts=[4]; c1:bw=33,experts=[0,4,6]; c6:bw=2,experts=[]; c9:bw=12,experts=[4]; c2:bw=21,experts=[4,6]; c7:bw=27,experts=[3,4]; c5:bw=11,experts=[5]; c4:bw=16,experts=[2]; c0:bw=6,experts=[]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>6.1698,5.9031,5.0233,7.5881,4.1107,4.3788,5.3112,7.0510,7.6573,5.4220</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:28:03</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.462552948886529</v>
+      </c>
+      <c r="F86" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G86" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="H86" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" t="n">
+        <v>62.3855</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:02.39</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>58.6914</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2.3961</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.2968</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5224.4904</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:27:04.49</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:22;2:26;8:40;6:24;1:32;4:24;9:33;3:29;5:7;7:6</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[1,3];2:[2,4];8:[0,4,5,6];6:[0,1];1:[4,5,6];4:[4,6];9:[4,5,6];3:[0,2];5:[];7:[]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=22,experts=[1,3]; c2:bw=26,experts=[2,4]; c8:bw=40,experts=[0,4,5,6]; c6:bw=24,experts=[0,1]; c1:bw=32,experts=[4,5,6]; c4:bw=24,experts=[4,6]; c9:bw=33,experts=[4,5,6]; c3:bw=29,experts=[0,2]; c5:bw=7,experts=[]; c7:bw=6,experts=[]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.4848,4.3923,6.1997,7.6178,5.0101,7.6984,4.1009,5.8916,7.0141,5.2817</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:29:05</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.455660865533953</v>
+      </c>
+      <c r="F87" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="G87" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="H87" t="n">
+        <v>82</v>
+      </c>
+      <c r="I87" t="n">
+        <v>62.2923</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:02.29</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>58.6562</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2.3223</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5286.8162</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:28:06.82</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:27;8:16;2:14;6:31;0:17;4:10;7:25;3:16;1:41;9:24</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[2,7];8:[7];2:[1];6:[2,4,6];0:[7];4:[7];7:[4,7];3:[1];1:[0,2,4,6];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[2,7]; c8:bw=16,experts=[7]; c2:bw=14,experts=[1]; c6:bw=31,experts=[2,4,6]; c0:bw=17,experts=[7]; c4:bw=10,experts=[7]; c7:bw=25,experts=[4,7]; c3:bw=16,experts=[1]; c1:bw=41,experts=[0,2,4,6]; c9:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>7.0774,6.1087,4.4784,7.5864,5.4390,7.6445,5.3020,5.8976,5.0155,4.1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:30:07</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.44442875911068</v>
+      </c>
+      <c r="F88" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="G88" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>87</v>
+      </c>
+      <c r="I88" t="n">
+        <v>62.187</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:02.19</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>58.575</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5349.0364</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:29:09.04</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:16;2:38;7:12;5:2;6:34;3:38;4:19;9:21;8:26;0:20</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[4];2:[0,4,6];7:[4];5:[];6:[4,6,7];3:[0,4,6];4:[1];9:[4,6];8:[4,6];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[4]; c2:bw=38,experts=[0,4,6]; c7:bw=12,experts=[4]; c5:bw=2,experts=[]; c6:bw=34,experts=[4,6,7]; c3:bw=38,experts=[0,4,6]; c4:bw=19,experts=[1]; c9:bw=21,experts=[4,6]; c8:bw=26,experts=[4,6]; c0:bw=20,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>5.0481,4.4125,5.3164,7.0594,7.5801,5.9029,7.5998,4.0924,6.1139,5.4497</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:31:09</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.448382460126253</v>
+      </c>
+      <c r="F89" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="G89" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="H89" t="n">
+        <v>87</v>
+      </c>
+      <c r="I89" t="n">
+        <v>62.2136</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:02.21</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>58.5749</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2.3308</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5411.283</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:30:11.28</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:24;6:15;3:19;7:23;0:35;4:21;9:17;1:16;5:17;2:26</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[3];3:[7];7:[4,6];0:[4,5,6];4:[0,4];9:[0];1:[7];5:[0];2:[3,4]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=24,experts=[4,6]; c6:bw=15,experts=[3]; c3:bw=19,experts=[7]; c7:bw=23,experts=[4,6]; c0:bw=35,experts=[4,5,6]; c4:bw=21,experts=[0,4]; c9:bw=17,experts=[0]; c1:bw=16,experts=[7]; c5:bw=17,experts=[0]; c2:bw=26,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>6.1550,7.5698,5.9004,5.3165,5.4552,7.6160,4.0893,5.0148,7.0615,4.3964</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:32:12</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.447158153781304</v>
+      </c>
+      <c r="F90" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="G90" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>87</v>
+      </c>
+      <c r="I90" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:02.15</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>58.5097</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2.3446</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.2944</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5473.467</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:31:13.47</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:17;8:42;2:25;9:34;7:12;5:26;0:7;6:18;4:17;1:23</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[5];8:[0,1,4,6];2:[4,6];9:[1,3,4];7:[0];5:[1,6];0:[];6:[4];4:[5];1:[1,4]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=17,experts=[5]; c8:bw=42,experts=[0,1,4,6]; c2:bw=25,experts=[4,6]; c9:bw=34,experts=[1,3,4]; c7:bw=12,experts=[0]; c5:bw=26,experts=[1,6]; c0:bw=7,experts=[]; c6:bw=18,experts=[4]; c4:bw=17,experts=[5]; c1:bw=23,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>5.9334,6.1759,4.3831,4.0929,5.3211,7.0944,5.3971,7.5346,7.6295,4.9475</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:33:14</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.428223910482474</v>
+      </c>
+      <c r="F91" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="G91" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H91" t="n">
+        <v>90</v>
+      </c>
+      <c r="I91" t="n">
+        <v>62.2284</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:02.23</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>58.5234</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2.3944</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.3094</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5535.7299</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:32:15.73</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:41;1:17;3:20;9:36;0:36;6:15;2:12;5:15;8:29;4:20</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[2,4,5,6];1:[4];3:[4,6];9:[4,6,7];0:[0,2,4];6:[4];2:[4];5:[3];8:[4,6];4:[3,4]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=41,experts=[2,4,5,6]; c1:bw=17,experts=[4]; c3:bw=20,experts=[4,6]; c9:bw=36,experts=[4,6,7]; c0:bw=36,experts=[0,2,4]; c6:bw=15,experts=[4]; c2:bw=12,experts=[4]; c5:bw=15,experts=[3]; c8:bw=29,experts=[4,6]; c4:bw=20,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>5.3817,5.0001,5.9153,4.1373,5.4316,7.5230,4.3140,7.0968,6.0857,7.6379</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:34:16</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.414463609430068</v>
+      </c>
+      <c r="F92" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="G92" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H92" t="n">
+        <v>90</v>
+      </c>
+      <c r="I92" t="n">
+        <v>62.2209</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:02.22</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>58.5772</v>
+      </c>
+      <c r="L92" t="n">
+        <v>2.3411</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.3014</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5597.9853</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:33:17.99</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:28;9:20;5:29;7:29;3:23;4:31;0:13;6:16;2:6;8:13</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[3,4];9:[2,4];5:[4,6];7:[1,4];3:[3,4];4:[0,4,6];0:[4];6:[5];2:[];8:[2]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[3,4]; c9:bw=20,experts=[2,4]; c5:bw=29,experts=[4,6]; c7:bw=29,experts=[1,4]; c3:bw=23,experts=[3,4]; c4:bw=31,experts=[0,4,6]; c0:bw=13,experts=[4]; c6:bw=16,experts=[5]; c2:bw=6,experts=[]; c8:bw=13,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>4.9721,4.1267,7.0894,5.3294,5.9026,7.6823,5.4306,7.5424,4.3749,6.1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:35:18</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.422146352704386</v>
+      </c>
+      <c r="F93" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="G93" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H93" t="n">
+        <v>90</v>
+      </c>
+      <c r="I93" t="n">
+        <v>62.0931</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:02.09</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>58.4785</v>
+      </c>
+      <c r="L93" t="n">
+        <v>2.2948</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.3185</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5660.1128</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:34:20.11</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:16;7:19;1:11;0:17;8:11;6:26;9:32;2:14;5:37;4:15</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[4];7:[3];1:[4];0:[4];8:[3];6:[4,6];9:[0,4,6];2:[5];5:[4,5,6];4:[2]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=16,experts=[4]; c7:bw=19,experts=[3]; c1:bw=11,experts=[4]; c0:bw=17,experts=[4]; c8:bw=11,experts=[3]; c6:bw=26,experts=[4,6]; c9:bw=32,experts=[0,4,6]; c2:bw=14,experts=[5]; c5:bw=37,experts=[4,5,6]; c4:bw=15,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>5.9149,5.2922,4.9754,5.4246,6.0988,7.5472,4.0904,4.3589,7.1067,7.6694</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:36:20</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.420233452815219</v>
+      </c>
+      <c r="F94" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="G94" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H94" t="n">
+        <v>90</v>
+      </c>
+      <c r="I94" t="n">
+        <v>62.1505</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:02.15</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>58.5499</v>
+      </c>
+      <c r="L94" t="n">
+        <v>2.3057</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.2935</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5722.2992</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:35:22.30</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:27;3:18;7:13;9:33;6:13;8:3;5:5;4:18;0:11;2:29</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[4,5];3:[2];7:[4];9:[4,5,6];6:[0];8:[];5:[];4:[4];0:[1];2:[2,7]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=27,experts=[4,5]; c3:bw=18,experts=[2]; c7:bw=13,experts=[4]; c9:bw=33,experts=[4,5,6]; c6:bw=13,experts=[0]; c8:bw=3,experts=[]; c5:bw=5,experts=[]; c4:bw=18,experts=[4]; c0:bw=11,experts=[1]; c2:bw=29,experts=[2,7]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>5.0504,5.8930,5.3296,4.1001,7.6068,6.1071,7.0188,7.6499,5.4153,4.3789</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:37:23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.417029623326944</v>
+      </c>
+      <c r="F95" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="G95" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H95" t="n">
+        <v>90</v>
+      </c>
+      <c r="I95" t="n">
+        <v>62.0426</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:02.04</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>58.3997</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2.3407</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.3008</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5784.3765</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:36:24.38</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:25;2:37;5:23;4:18;6:17;9:28;1:40;8:4;0:31;3:19</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[4,7];2:[1,4,6];5:[2,7];4:[7];6:[1];9:[4,6];1:[0,2,4,6];8:[];0:[3,4,7];3:[1]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=25,experts=[4,7]; c2:bw=37,experts=[1,4,6]; c5:bw=23,experts=[2,7]; c4:bw=18,experts=[7]; c6:bw=17,experts=[1]; c9:bw=28,experts=[4,6]; c1:bw=40,experts=[0,2,4,6]; c8:bw=4,experts=[]; c0:bw=31,experts=[3,4,7]; c3:bw=19,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>5.3480,4.3789,7.0547,7.6147,7.5093,4.1043,5.0093,6.0840,5.3825,5.9140</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:38:25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.41484348306517</v>
+      </c>
+      <c r="F96" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="G96" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="H96" t="n">
+        <v>90</v>
+      </c>
+      <c r="I96" t="n">
+        <v>62.3544</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:02.35</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>58.7236</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2.3138</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.3157</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5846.7666</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:37:26.77</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:34;9:24;4:9;6:23;0:20;3:23;1:18;8:43;2:13;5:5</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[4,5,6];9:[4,6];4:[];6:[2,7];0:[4,6];3:[0,4];1:[4];8:[4,5,6,7];2:[0];5:[]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=34,experts=[4,5,6]; c9:bw=24,experts=[4,6]; c4:bw=9,experts=[]; c6:bw=23,experts=[2,7]; c0:bw=20,experts=[4,6]; c3:bw=23,experts=[0,4]; c1:bw=18,experts=[4]; c8:bw=43,experts=[4,5,6,7]; c2:bw=13,experts=[0]; c5:bw=5,experts=[]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>5.3647,4.1145,7.7264,7.5454,5.4342,5.8972,5.0129,6.1333,4.3985,7.0964</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:39:27</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.395448602839049</v>
+      </c>
+      <c r="F97" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="G97" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>62.4175</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:02.42</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>58.7147</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2.4096</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.2919</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5909.2194</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:38:29.22</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:37;9:25;3:26;1:20;5:34;4:28;6:18;7:29;0:20;8:36</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[3,4,6];9:[4,6];3:[4,7];1:[4,7];5:[0,4,6];4:[1,4];6:[3];7:[4,6];0:[4,5];8:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=37,experts=[3,4,6]; c9:bw=25,experts=[4,6]; c3:bw=26,experts=[4,7]; c1:bw=20,experts=[4,7]; c5:bw=34,experts=[0,4,6]; c4:bw=28,experts=[1,4]; c6:bw=18,experts=[3]; c7:bw=29,experts=[4,6]; c0:bw=20,experts=[4,5]; c8:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>4.4178,4.1655,5.9515,5.0157,7.1156,7.7016,7.4879,5.2953,5.4240,6.1398</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:40:30</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.398947969957833</v>
+      </c>
+      <c r="F98" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>96</v>
+      </c>
+      <c r="I98" t="n">
+        <v>62.435</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:02.43</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>58.7837</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2.3415</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.3086</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5971.6913</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:39:31.69</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:23;9:24;8:24;4:9;7:17;1:28;3:20;5:26;6:28;2:31</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[4,6];9:[1,3];8:[1,4];4:[];7:[0];1:[1,4];3:[4,5];5:[1,4];6:[4,6];2:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=23,experts=[4,6]; c9:bw=24,experts=[1,3]; c8:bw=24,experts=[1,4]; c4:bw=9,experts=[]; c7:bw=17,experts=[0]; c1:bw=28,experts=[1,4]; c3:bw=20,experts=[4,5]; c5:bw=26,experts=[1,4]; c6:bw=28,experts=[4,6]; c2:bw=31,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.4833,4.1363,6.1234,7.6792,5.3452,5.0124,5.9362,7.0874,7.5844,4.3960</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:41:32</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.404997142098264</v>
+      </c>
+      <c r="F99" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="G99" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="H99" t="n">
+        <v>96</v>
+      </c>
+      <c r="I99" t="n">
+        <v>62.3083</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:02.31</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>58.6913</v>
+      </c>
+      <c r="L99" t="n">
+        <v>2.3311</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.2846</v>
+      </c>
+      <c r="N99" t="n">
+        <v>6034.0345</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:40:34.03</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:29;8:30;9:15;7:13;6:21;5:28;0:19;3:14;1:15;2:14</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[3,5];8:[1,4,6];9:[7];7:[2];6:[4,6];5:[3,4];0:[0];3:[6];1:[4];2:[4]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[3,5]; c8:bw=30,experts=[1,4,6]; c9:bw=15,experts=[7]; c7:bw=13,experts=[2]; c6:bw=21,experts=[4,6]; c5:bw=28,experts=[3,4]; c0:bw=19,experts=[0]; c3:bw=14,experts=[6]; c1:bw=15,experts=[4]; c2:bw=14,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.7260,6.1418,4.0973,5.3328,7.5754,7.0743,5.4702,5.9206,4.9833,4.3696</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:42:35</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.385741534502805</v>
+      </c>
+      <c r="F100" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="G100" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>96</v>
+      </c>
+      <c r="I100" t="n">
+        <v>62.3947</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:02.39</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>58.7293</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.3181</v>
+      </c>
+      <c r="N100" t="n">
+        <v>6096.4649</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:41:36.46</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:19;5:28;7:26;1:34;3:21;9:12;4:14;0:23;2:17;6:20</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[2];5:[4,6];7:[1,4];1:[3,4,6];3:[3,4];9:[2];4:[0];0:[2,4];2:[4];6:[4,5]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=19,experts=[2]; c5:bw=28,experts=[4,6]; c7:bw=26,experts=[1,4]; c1:bw=34,experts=[3,4,6]; c3:bw=21,experts=[3,4]; c9:bw=12,experts=[2]; c4:bw=14,experts=[0]; c0:bw=23,experts=[2,4]; c2:bw=17,experts=[4]; c6:bw=20,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>6.1451,7.1287,5.3427,5.0551,5.9114,4.0930,7.6749,5.4175,4.3579,7.6028</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:43:37</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.378574136191594</v>
+      </c>
+      <c r="F101" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="G101" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="H101" t="n">
+        <v>100</v>
+      </c>
+      <c r="I101" t="n">
+        <v>62.545</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:02.54</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>58.8849</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2.3428</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.3159</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6159.0463</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:42:39.05</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:17;8:25;9:30;5:10;6:25;1:10;4:37;7:4;3:24;0:36</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[4];8:[3,4];9:[0,4,6];5:[5];6:[4,6];1:[4];4:[2,4,6];7:[];3:[4,6];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=17,experts=[4]; c8:bw=25,experts=[3,4]; c9:bw=30,experts=[0,4,6]; c5:bw=10,experts=[5]; c6:bw=25,experts=[4,6]; c1:bw=10,experts=[4]; c4:bw=37,experts=[2,4,6]; c7:bw=4,experts=[]; c3:bw=24,experts=[4,6]; c0:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>4.4203,6.1860,4.1313,7.1176,7.5869,5.0472,7.7401,5.3047,5.8803,5.4705</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
